--- a/data/trans_orig/P42-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P42-Habitat-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2007</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2007 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>512</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>509136</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>485602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>529690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>485232</t>
+          <t>485602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>530204</t>
+          <t>529690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>509136</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>485232</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>530204</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>77,74%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172878</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151810</t>
+          <t>152324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196782</t>
+          <t>196412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>172878</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>151810</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>196782</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>22,26%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>28,85%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>690</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682014</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>682014</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>682014</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>682014</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>702</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>753919</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>726389</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>777689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>727032</t>
+          <t>726389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>781134</t>
+          <t>777689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>753919</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>727032</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>781134</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>211930</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184715</t>
+          <t>188160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238817</t>
+          <t>239460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>211930</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>184715</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>238817</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>21,94%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>906</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965849</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965849</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>965849</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>965849</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>965849</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>569315</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>550384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>588931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>549304</t>
+          <t>550384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>588148</t>
+          <t>588931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>569315</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>549304</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>588148</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>80,33%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114526</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95693</t>
+          <t>94910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134537</t>
+          <t>133457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>114526</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>95693</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>134537</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>696</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>793</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>828986</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>801296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>852030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>803729</t>
+          <t>801296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>854342</t>
+          <t>852030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>828986</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>803729</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>854342</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>80,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>77,85%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>82,75%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203408</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178052</t>
+          <t>180364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>228665</t>
+          <t>231098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>203408</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>178052</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>228665</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>19,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>992</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032394</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032394</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1032394</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1032394</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1032394</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2609848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2707448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2615119</t>
+          <t>2609848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2706419</t>
+          <t>2707448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2661356</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2615119</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2706419</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>77,74%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>80,45%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>702743</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>656651</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>754251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>657680</t>
+          <t>656651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>748980</t>
+          <t>754251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>702743</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>657680</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>748980</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>22,26%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3364099</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3364099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3364099</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3284</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3364099</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3364099</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3364099</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2433,14 +1848,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2454,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,25 +1887,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2012</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2012 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +1909,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2511,17 +1918,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2592,41 +1988,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2649,13 +2010,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2670,37 +2024,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>594315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>575399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>573509</t>
+          <t>575399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>610470</t>
+          <t>611405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,47 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>594315</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>573509</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>610470</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>85,62%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>82,62%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>87,95%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -2783,37 +2102,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99815</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83660</t>
+          <t>82725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120621</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,47 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>99815</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>83660</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>120621</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>14,38%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>17,38%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2896,37 +2180,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694130</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2960,41 +2244,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>694130</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>694130</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>694130</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3013,37 +2262,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>790</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>870924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>845925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>890995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>843186</t>
+          <t>845925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>892900</t>
+          <t>890995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,47 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>870924</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>843186</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>892900</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>84,93%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>82,23%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>87,08%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -3126,37 +2340,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154494</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132518</t>
+          <t>134423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182232</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,47 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>154494</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>132518</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>182232</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>15,07%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>17,77%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -3239,37 +2418,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>934</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1025418</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1025418</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1025418</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3303,41 +2482,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1025418</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1025418</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1025418</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3356,37 +2500,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>627</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695469</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>675625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>710697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>679300</t>
+          <t>675625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>711995</t>
+          <t>710697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,47 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>695469</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>679300</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>711995</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>92,12%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -3469,37 +2578,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60936</t>
+          <t>62234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93631</t>
+          <t>97306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,47 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>77462</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>60936</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>93631</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -3582,37 +2656,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>701</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>772931</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>772931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>772931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3646,41 +2720,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>772931</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>772931</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>772931</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3699,37 +2738,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>878</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>922492</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>898447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>941685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>902481</t>
+          <t>898447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>944458</t>
+          <t>941685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,47 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>922492</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>902481</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>944458</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>86,39%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -3812,37 +2816,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122223</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100257</t>
+          <t>103030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142234</t>
+          <t>146268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,47 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>122223</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>100257</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>142234</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -3925,37 +2894,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>996</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1044715</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1044715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1044715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3989,41 +2958,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1044715</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1044715</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1044715</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4042,37 +2976,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3083200</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3041580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3124401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3044776</t>
+          <t>3041580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3122790</t>
+          <t>3124401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,47 +3036,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3083200</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3044776</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3122790</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>86,08%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3054,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>431</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>453993</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>495613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414403</t>
+          <t>412792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492417</t>
+          <t>495613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,47 +3114,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>453993</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>414403</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>492417</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4268,37 +3132,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3537193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3537193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3537193</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4332,41 +3196,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3537193</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3537193</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3537193</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4380,14 +3209,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4401,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4420,25 +3248,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2016</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +3270,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4458,17 +3279,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4539,41 +3349,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4596,13 +3371,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4617,37 +3385,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>548</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>553405</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>532856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>572247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>531555</t>
+          <t>532856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>571230</t>
+          <t>572247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>553405</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>531555</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>571230</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>79,39%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -4730,37 +3463,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116172</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98347</t>
+          <t>97330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138022</t>
+          <t>136721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>116172</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>98347</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>138022</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3541,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>663</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669577</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4907,41 +3605,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>669577</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>669577</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>669577</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4960,37 +3623,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>851</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>913510</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>892190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>933272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>893477</t>
+          <t>892190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>932806</t>
+          <t>933272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,47 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>913510</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>893477</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>932806</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>88,38%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>90,24%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -5073,37 +3701,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120133</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100837</t>
+          <t>100371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140166</t>
+          <t>141453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,47 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>120133</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>100837</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>140166</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3779,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>969</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5250,41 +3843,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1033643</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1033643</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1033643</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5303,37 +3861,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>637</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>676852</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>657183</t>
+          <t>655517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>695747</t>
+          <t>694984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,47 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>676852</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>657183</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>695747</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>86,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>84,4%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -5416,37 +3939,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101814</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>83682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121483</t>
+          <t>123149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,47 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>101814</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>82919</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>121483</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4017,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>730</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>778666</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>778666</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>778666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5593,41 +4081,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>778666</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>778666</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>778666</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5646,37 +4099,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>846</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>922787</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>901302</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>942083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>900425</t>
+          <t>901302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>943260</t>
+          <t>942083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,47 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>922787</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>900425</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>943260</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>89,14%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -5759,37 +4177,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112421</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91948</t>
+          <t>93125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134783</t>
+          <t>133906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,47 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>112421</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>91948</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>134783</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -5872,37 +4255,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>951</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1035208</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1035208</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1035208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5936,41 +4319,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1035208</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1035208</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1035208</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5989,37 +4337,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3066554</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3023913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3102832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3028943</t>
+          <t>3023913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3109819</t>
+          <t>3102832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,47 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3066554</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3028943</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3109819</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -6102,37 +4415,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>431</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>450541</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>493182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407276</t>
+          <t>414263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>488152</t>
+          <t>493182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,47 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>450541</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>407276</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>488152</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -6215,37 +4493,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3517095</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3517095</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3517095</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6279,41 +4557,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3313</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3517095</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3517095</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3517095</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6327,14 +4570,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -6348,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6367,25 +4609,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha acudido alguna vez al ginecólogo en 2023</t>
+          <t>Población según si ha acudido alguna vez al ginecólogo en 2023 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +4631,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6405,17 +4640,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -6486,41 +4710,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -6543,13 +4732,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6564,37 +4746,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>786</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410800</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +4791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>392147</t>
+          <t>393694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424981</t>
+          <t>424299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,47 +4806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>410800</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>392147</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>424981</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>77,5%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>83,99%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -6677,37 +4824,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95200</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +4869,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81019</t>
+          <t>81701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113853</t>
+          <t>112306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,47 +4884,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>95200</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>81019</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>113853</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -6790,37 +4902,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>937</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>506000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6854,41 +4966,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>506000</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>506000</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>506000</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6907,37 +4984,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>622026</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>642001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +5029,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>600198</t>
+          <t>602885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>639136</t>
+          <t>642001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,47 +5044,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>622026</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>600198</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>639136</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>81,6%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -7020,37 +5062,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113555</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96445</t>
+          <t>93580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135383</t>
+          <t>132696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,47 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>113555</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>96445</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>135383</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -7133,37 +5140,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>735581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>735581</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>735581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7197,41 +5204,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1177</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>735581</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>735581</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>735581</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7250,37 +5222,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471024</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>664289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +5267,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203893</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>662892</t>
+          <t>664289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,47 +5282,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>471024</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>203893</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>662892</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>90,86%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -7363,37 +5300,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258571</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +5345,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66703</t>
+          <t>65306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525702</t>
+          <t>517025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,47 +5360,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>258571</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>66703</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>525702</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>72,05%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -7476,37 +5378,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729595</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729595</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7540,41 +5442,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>729595</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>729595</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>729595</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7593,37 +5460,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>716265</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>750536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +5505,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>690332</t>
+          <t>689422</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>752214</t>
+          <t>750536</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,47 +5520,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>716265</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>690332</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>752214</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>87,97%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -7706,37 +5538,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +5583,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>104587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164791</t>
+          <t>165701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,47 +5598,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>138858</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>102909</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>164791</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -7819,37 +5616,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855123</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7883,41 +5680,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>855123</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>855123</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>855123</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7936,37 +5698,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2220114</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1720767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2411873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +5743,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1683901</t>
+          <t>1720767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2407647</t>
+          <t>2411873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,47 +5758,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2220114</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1683901</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2407647</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>85,19%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -8049,37 +5776,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>606184</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1105531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +5821,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>418651</t>
+          <t>414425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1142397</t>
+          <t>1105531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,47 +5836,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>606184</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>418651</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1142397</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>40,42%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -8162,37 +5854,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2826298</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2826298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2826298</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8226,41 +5918,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>4028</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2826298</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2826298</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2826298</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8274,14 +5931,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P42-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P42-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>485602</t>
+          <t>489402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>529690</t>
+          <t>532751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>485602</t>
+          <t>489402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>529690</t>
+          <t>532751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,11%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152324</t>
+          <t>149263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196412</t>
+          <t>192612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152324</t>
+          <t>149263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196412</t>
+          <t>192612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>726389</t>
+          <t>725795</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>777689</t>
+          <t>779901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>726389</t>
+          <t>725795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>777689</t>
+          <t>779901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188160</t>
+          <t>185948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239460</t>
+          <t>240054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188160</t>
+          <t>185948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239460</t>
+          <t>240054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>550384</t>
+          <t>549183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>588931</t>
+          <t>586458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>550384</t>
+          <t>549183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>588931</t>
+          <t>586458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94910</t>
+          <t>97383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133457</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94910</t>
+          <t>97383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133457</t>
+          <t>134658</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>801296</t>
+          <t>801712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>852030</t>
+          <t>854916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>801296</t>
+          <t>801712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>852030</t>
+          <t>854916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,81%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180364</t>
+          <t>177478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>231098</t>
+          <t>230682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180364</t>
+          <t>177478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231098</t>
+          <t>230682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2609848</t>
+          <t>2613736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2707448</t>
+          <t>2708203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>656651</t>
+          <t>655896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754251</t>
+          <t>750363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>575399</t>
+          <t>574215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>611405</t>
+          <t>611940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>575399</t>
+          <t>574215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>611405</t>
+          <t>611940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82725</t>
+          <t>82190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118731</t>
+          <t>119915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82725</t>
+          <t>82190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118731</t>
+          <t>119915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>845925</t>
+          <t>845573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>890995</t>
+          <t>893115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>845925</t>
+          <t>845573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>890995</t>
+          <t>893115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134423</t>
+          <t>132303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179493</t>
+          <t>179845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134423</t>
+          <t>132303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179493</t>
+          <t>179845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>675625</t>
+          <t>675591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>710697</t>
+          <t>711836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>675625</t>
+          <t>675591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>710697</t>
+          <t>711836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62234</t>
+          <t>61095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97306</t>
+          <t>97340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62234</t>
+          <t>61095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97306</t>
+          <t>97340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>898447</t>
+          <t>899978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>941685</t>
+          <t>942183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>898447</t>
+          <t>899978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>941685</t>
+          <t>942183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103030</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146268</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103030</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146268</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3041580</t>
+          <t>3039240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3124401</t>
+          <t>3120170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3041580</t>
+          <t>3039240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3124401</t>
+          <t>3120170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>412792</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495613</t>
+          <t>497953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>412792</t>
+          <t>417023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495613</t>
+          <t>497953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3395,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>532856</t>
+          <t>532824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>572247</t>
+          <t>570541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>532856</t>
+          <t>532824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>572247</t>
+          <t>570541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97330</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136721</t>
+          <t>136753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97330</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136721</t>
+          <t>136753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>892190</t>
+          <t>889544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>933272</t>
+          <t>932303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>892190</t>
+          <t>889544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>933272</t>
+          <t>932303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100371</t>
+          <t>101340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141453</t>
+          <t>144099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100371</t>
+          <t>101340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>141453</t>
+          <t>144099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>655517</t>
+          <t>655903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>694984</t>
+          <t>696313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>655517</t>
+          <t>655903</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>694984</t>
+          <t>696313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>82353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>122763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83682</t>
+          <t>82353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>122763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>901302</t>
+          <t>900009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>942083</t>
+          <t>941514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>901302</t>
+          <t>900009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>942083</t>
+          <t>941514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>93694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133906</t>
+          <t>135199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93125</t>
+          <t>93694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133906</t>
+          <t>135199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3023913</t>
+          <t>3023962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3105291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3023913</t>
+          <t>3023962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3102832</t>
+          <t>3105291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>493182</t>
+          <t>493133</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414263</t>
+          <t>411804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493182</t>
+          <t>493133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4751,32 +4751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>410800</t>
+          <t>442874</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>393694</t>
+          <t>424528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>424299</t>
+          <t>459401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4786,32 +4786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>410800</t>
+          <t>442874</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>393694</t>
+          <t>424528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>424299</t>
+          <t>459401</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95200</t>
+          <t>105345</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81701</t>
+          <t>88818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112306</t>
+          <t>123691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4864,32 +4864,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95200</t>
+          <t>105345</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81701</t>
+          <t>88818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112306</t>
+          <t>123691</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>548219</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>548219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>548219</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>548219</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>548219</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>548219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4989,32 +4989,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>622026</t>
+          <t>693959</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>602885</t>
+          <t>670249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>642001</t>
+          <t>715239</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5024,32 +5024,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>622026</t>
+          <t>693959</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>602885</t>
+          <t>670249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>642001</t>
+          <t>715239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -5067,32 +5067,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113555</t>
+          <t>126937</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>105657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>150647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5102,32 +5102,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>113555</t>
+          <t>126937</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>105657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>150647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>735581</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>735581</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>735581</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>735581</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>735581</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>735581</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5227,32 +5227,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>471024</t>
+          <t>508954</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>489078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>664289</t>
+          <t>525257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5262,32 +5262,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>471024</t>
+          <t>508954</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>489078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>664289</t>
+          <t>525257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -5305,32 +5305,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>258571</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517025</t>
+          <t>84036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5340,32 +5340,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>258571</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>517025</t>
+          <t>84036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -5383,17 +5383,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>573114</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>573114</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>573114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>573114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>573114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>573114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5465,32 +5465,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>716265</t>
+          <t>697987</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>689422</t>
+          <t>673801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>750536</t>
+          <t>722255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5500,32 +5500,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>716265</t>
+          <t>697987</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>689422</t>
+          <t>673801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>750536</t>
+          <t>722255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -5543,32 +5543,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>138858</t>
+          <t>159558</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104587</t>
+          <t>135290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165701</t>
+          <t>183744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5578,32 +5578,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138858</t>
+          <t>159558</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104587</t>
+          <t>135290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165701</t>
+          <t>183744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>855123</t>
+          <t>857545</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>855123</t>
+          <t>857545</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>855123</t>
+          <t>857545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>855123</t>
+          <t>857545</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>855123</t>
+          <t>857545</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>855123</t>
+          <t>857545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1720767</t>
+          <t>2301184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2411873</t>
+          <t>2381376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5738,32 +5738,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1720767</t>
+          <t>2301184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2411873</t>
+          <t>2381376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -5781,32 +5781,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>414425</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1105531</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>606184</t>
+          <t>456000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414425</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1105531</t>
+          <t>498590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2826298</t>
+          <t>2799774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
